--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>107620286</v>
       </c>
       <c r="B2" t="n">
-        <v>56876</v>
+        <v>57893</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rapport ska skrivas (för Rrk)</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525630.7440169689</v>
+        <v>525631</v>
       </c>
       <c r="R2" t="n">
-        <v>6227461.919962233</v>
+        <v>6227462</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107620286</v>
       </c>
       <c r="B2" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107620286</v>
       </c>
       <c r="B2" t="n">
-        <v>57894</v>
+        <v>57988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107620286</v>
       </c>
       <c r="B2" t="n">
-        <v>57991</v>
+        <v>57997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107620286</v>
       </c>
       <c r="B2" t="n">
-        <v>57997</v>
+        <v>58000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107620286</v>
       </c>
       <c r="B2" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2023 artfynd.xlsx
+++ b/artfynd/A 12131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107620286</v>
+        <v>107620209</v>
       </c>
       <c r="B2" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>233849</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svarthakad buskskvätta</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubicola</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -771,11 +770,6 @@
           <t>11:10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Såg en hanne som höll til i buskridån ca 200m innan det ensamma röda huset höger sida längs Östranäsvägen.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -797,6 +791,126 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107620286</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58472</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>233849</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svarthakad buskskvätta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxicola rubicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östranäsvägen, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>525631</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6227462</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Listerby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Såg en hanne som höll til i buskridån ca 200m innan det ensamma röda huset höger sida längs Östranäsvägen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Pisch</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Pisch</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
